--- a/weeks/◆ 2026년 10월 2주 편성표 (1005 ~ 1011) (3).xlsx
+++ b/weeks/◆ 2026년 10월 2주 편성표 (1005 ~ 1011) (3).xlsx
@@ -508,48 +508,48 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="6.0"/>
-    <col min="2" max="2" customWidth="true" width="0.375"/>
-    <col min="3" max="3" customWidth="true" width="5.125"/>
-    <col min="4" max="4" customWidth="true" width="3.625"/>
-    <col min="5" max="5" customWidth="true" width="2.125"/>
-    <col min="6" max="6" customWidth="true" width="3.625"/>
-    <col min="7" max="7" customWidth="true" width="16.375"/>
-    <col min="8" max="8" customWidth="true" width="0.375"/>
-    <col min="9" max="9" customWidth="true" width="5.125"/>
-    <col min="10" max="10" customWidth="true" width="3.625"/>
-    <col min="11" max="11" customWidth="true" width="2.125"/>
-    <col min="12" max="12" customWidth="true" width="3.625"/>
-    <col min="13" max="13" customWidth="true" width="16.375"/>
-    <col min="14" max="14" customWidth="true" width="0.375"/>
-    <col min="15" max="15" customWidth="true" width="5.125"/>
-    <col min="16" max="16" customWidth="true" width="3.625"/>
-    <col min="17" max="17" customWidth="true" width="2.125"/>
-    <col min="18" max="18" customWidth="true" width="3.625"/>
-    <col min="19" max="19" customWidth="true" width="16.375"/>
-    <col min="20" max="20" customWidth="true" width="0.375"/>
-    <col min="21" max="21" customWidth="true" width="5.125"/>
-    <col min="22" max="22" customWidth="true" width="3.625"/>
-    <col min="23" max="23" customWidth="true" width="2.125"/>
-    <col min="24" max="24" customWidth="true" width="3.625"/>
-    <col min="25" max="25" customWidth="true" width="16.375"/>
-    <col min="26" max="26" customWidth="true" width="0.375"/>
-    <col min="27" max="27" customWidth="true" width="5.125"/>
-    <col min="28" max="28" customWidth="true" width="3.625"/>
-    <col min="29" max="29" customWidth="true" width="2.125"/>
-    <col min="30" max="30" customWidth="true" width="3.625"/>
-    <col min="31" max="31" customWidth="true" width="16.375"/>
-    <col min="32" max="32" customWidth="true" width="0.375"/>
-    <col min="33" max="33" customWidth="true" width="5.125"/>
-    <col min="34" max="34" customWidth="true" width="3.625"/>
-    <col min="35" max="35" customWidth="true" width="2.125"/>
-    <col min="36" max="36" customWidth="true" width="3.625"/>
-    <col min="37" max="37" customWidth="true" width="16.375"/>
-    <col min="38" max="38" customWidth="true" width="0.375"/>
-    <col min="39" max="39" customWidth="true" width="5.125"/>
-    <col min="40" max="40" customWidth="true" width="3.625"/>
-    <col min="41" max="41" customWidth="true" width="2.125"/>
-    <col min="42" max="42" customWidth="true" width="3.625"/>
-    <col min="43" max="43" customWidth="true" width="16.625"/>
+    <col min="2" max="2" customWidth="true" width="0.25"/>
+    <col min="3" max="3" customWidth="true" width="3.75"/>
+    <col min="4" max="4" customWidth="true" width="2.625"/>
+    <col min="5" max="5" customWidth="true" width="1.5"/>
+    <col min="6" max="6" customWidth="true" width="2.625"/>
+    <col min="7" max="7" customWidth="true" width="11.875"/>
+    <col min="8" max="8" customWidth="true" width="0.25"/>
+    <col min="9" max="9" customWidth="true" width="3.75"/>
+    <col min="10" max="10" customWidth="true" width="2.625"/>
+    <col min="11" max="11" customWidth="true" width="1.5"/>
+    <col min="12" max="12" customWidth="true" width="2.625"/>
+    <col min="13" max="13" customWidth="true" width="11.875"/>
+    <col min="14" max="14" customWidth="true" width="0.25"/>
+    <col min="15" max="15" customWidth="true" width="3.75"/>
+    <col min="16" max="16" customWidth="true" width="2.625"/>
+    <col min="17" max="17" customWidth="true" width="1.5"/>
+    <col min="18" max="18" customWidth="true" width="2.625"/>
+    <col min="19" max="19" customWidth="true" width="11.875"/>
+    <col min="20" max="20" customWidth="true" width="0.25"/>
+    <col min="21" max="21" customWidth="true" width="3.75"/>
+    <col min="22" max="22" customWidth="true" width="2.625"/>
+    <col min="23" max="23" customWidth="true" width="1.5"/>
+    <col min="24" max="24" customWidth="true" width="2.625"/>
+    <col min="25" max="25" customWidth="true" width="11.875"/>
+    <col min="26" max="26" customWidth="true" width="0.25"/>
+    <col min="27" max="27" customWidth="true" width="3.75"/>
+    <col min="28" max="28" customWidth="true" width="2.625"/>
+    <col min="29" max="29" customWidth="true" width="1.5"/>
+    <col min="30" max="30" customWidth="true" width="2.625"/>
+    <col min="31" max="31" customWidth="true" width="11.875"/>
+    <col min="32" max="32" customWidth="true" width="0.25"/>
+    <col min="33" max="33" customWidth="true" width="3.75"/>
+    <col min="34" max="34" customWidth="true" width="2.625"/>
+    <col min="35" max="35" customWidth="true" width="1.5"/>
+    <col min="36" max="36" customWidth="true" width="2.625"/>
+    <col min="37" max="37" customWidth="true" width="11.875"/>
+    <col min="38" max="38" customWidth="true" width="0.25"/>
+    <col min="39" max="39" customWidth="true" width="3.75"/>
+    <col min="40" max="40" customWidth="true" width="2.625"/>
+    <col min="41" max="41" customWidth="true" width="1.5"/>
+    <col min="42" max="42" customWidth="true" width="2.625"/>
+    <col min="43" max="43" customWidth="true" width="11.625"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="true" ht="24.75">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AK9" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">보넬드 당근주스 </t>
+          <t>(재) 이경제 흑염소진액</t>
         </is>
       </c>
       <c r="AL9" s="25"/>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="AQ13" s="30" t="inlineStr">
         <is>
-          <t>유피토스 염색제</t>
+          <t>유피토스 트리트먼트</t>
         </is>
       </c>
     </row>
@@ -2610,17 +2610,17 @@
       </c>
       <c r="E17" s="24" t="inlineStr">
         <is>
-          <t>대</t>
+          <t>중</t>
         </is>
       </c>
       <c r="F17" s="30" t="inlineStr">
         <is>
-          <t>'금융상품'</t>
-        </is>
-      </c>
-      <c r="G17" s="36" t="inlineStr">
-        <is>
-          <t>#금융상품</t>
+          <t>언더웨어</t>
+        </is>
+      </c>
+      <c r="G17" s="30" t="inlineStr">
+        <is>
+          <t>라코스테드로즈</t>
         </is>
       </c>
       <c r="H17" s="25"/>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="AL17" s="25"/>
-      <c r="AM17" s="37" t="inlineStr">
+      <c r="AM17" s="29" t="inlineStr">
         <is>
           <t>16:10</t>
         </is>
@@ -2767,19 +2767,20 @@
           <t>65</t>
         </is>
       </c>
-      <c r="AO17" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="AO17" s="31" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="AP17" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AQ17" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'리빙'</t>
+        </is>
+      </c>
+      <c r="AQ17" s="30" t="inlineStr">
+        <is>
+          <t>플로너스디퓨저</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2813,7 @@
       </c>
       <c r="G18" s="30" t="inlineStr">
         <is>
-          <t>디아루체 글리터 뷔스티에 3종</t>
+          <t>에바큐브 캐시미어 베스트</t>
         </is>
       </c>
       <c r="H18" s="25"/>
@@ -3092,7 +3093,7 @@
           <t>16:30</t>
         </is>
       </c>
-      <c r="AB19" s="34" t="inlineStr">
+      <c r="AB19" s="24" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -3107,7 +3108,7 @@
           <t>'패션2Lab'</t>
         </is>
       </c>
-      <c r="AE19" s="40" t="inlineStr">
+      <c r="AE19" s="30" t="inlineStr">
         <is>
           <t>이상봉 넥카프 3종</t>
         </is>
@@ -3277,12 +3278,12 @@
         </is>
       </c>
       <c r="Z20" s="25"/>
-      <c r="AA20" s="29" t="inlineStr">
+      <c r="AA20" s="37" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="AB20" s="34" t="inlineStr">
+      <c r="AB20" s="24" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -3294,12 +3295,12 @@
       </c>
       <c r="AD20" s="30" t="inlineStr">
         <is>
-          <t>'패션3Lab'</t>
-        </is>
-      </c>
-      <c r="AE20" s="40" t="inlineStr">
-        <is>
-          <t>머티리얼랩 레이스 니트 집업 外</t>
+          <t>Hit &amp; Best</t>
+        </is>
+      </c>
+      <c r="AE20" s="38" t="inlineStr">
+        <is>
+          <t>Hit &amp; Best</t>
         </is>
       </c>
       <c r="AF20" s="25"/>
@@ -3473,7 +3474,7 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="AB21" s="24" t="inlineStr">
+      <c r="AB21" s="34" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -3485,12 +3486,12 @@
       </c>
       <c r="AD21" s="30" t="inlineStr">
         <is>
-          <t>'잡화'</t>
-        </is>
-      </c>
-      <c r="AE21" s="30" t="inlineStr">
-        <is>
-          <t>슈올즈 포브</t>
+          <t>'패션3Lab'</t>
+        </is>
+      </c>
+      <c r="AE21" s="40" t="inlineStr">
+        <is>
+          <t>머티리얼랩 레이스 니트 집업 外</t>
         </is>
       </c>
       <c r="AF21" s="25"/>
@@ -3666,7 +3667,7 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="AB22" s="24" t="inlineStr">
+      <c r="AB22" s="34" t="inlineStr">
         <is>
           <t>75</t>
         </is>
@@ -3682,7 +3683,7 @@
           <t>'패션2Lab'</t>
         </is>
       </c>
-      <c r="AE22" s="30" t="inlineStr">
+      <c r="AE22" s="40" t="inlineStr">
         <is>
           <t>리오벨 26 pre-winter 풀스킨 렉스퍼 야상 자켓</t>
         </is>
@@ -3782,7 +3783,7 @@
       </c>
       <c r="J23" s="32" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K23" s="24" t="inlineStr">
@@ -3907,7 +3908,7 @@
         </is>
       </c>
       <c r="AL23" s="25"/>
-      <c r="AM23" s="37" t="inlineStr">
+      <c r="AM23" s="29" t="inlineStr">
         <is>
           <t>22:45</t>
         </is>
@@ -3919,17 +3920,17 @@
       </c>
       <c r="AO23" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>대</t>
         </is>
       </c>
       <c r="AP23" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AQ23" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="AQ23" s="39" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
         </is>
       </c>
     </row>
@@ -3952,28 +3953,28 @@
       </c>
       <c r="E24" s="24" t="inlineStr">
         <is>
-          <t>대</t>
+          <t>수</t>
         </is>
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="G24" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'가전'</t>
+        </is>
+      </c>
+      <c r="G24" s="42" t="inlineStr">
+        <is>
+          <t>황쇼 다이슨에어랩</t>
         </is>
       </c>
       <c r="H24" s="25"/>
       <c r="I24" s="29" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="J24" s="32" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K24" s="24" t="inlineStr">

--- a/weeks/◆ 2026년 10월 2주 편성표 (1005 ~ 1011) (3).xlsx
+++ b/weeks/◆ 2026년 10월 2주 편성표 (1005 ~ 1011) (3).xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="38">
+  <fonts count="36">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -236,20 +236,8 @@
       <color rgb="00333333"/>
       <u val="none"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="9.0"/>
-      <color rgb="00333333"/>
-      <u val="none"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="9.0"/>
-      <color rgb="00333333"/>
-      <u val="none"/>
-    </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -289,11 +277,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FDFFBD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EEEEEE"/>
       </patternFill>
     </fill>
     <fill>
@@ -366,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="true" applyNumberFormat="true">
       <alignment wrapText="true"/>
@@ -476,22 +459,16 @@
     <xf numFmtId="49" fontId="31" fillId="8" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="32" fillId="9" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+    <xf numFmtId="49" fontId="32" fillId="8" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+      <alignment wrapText="true" horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="9" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="9" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="8" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+    <xf numFmtId="49" fontId="34" fillId="6" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="35" fillId="7" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="10" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="6" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2294,7 +2271,7 @@
         </is>
       </c>
       <c r="T15" s="25"/>
-      <c r="U15" s="37" t="inlineStr">
+      <c r="U15" s="29" t="inlineStr">
         <is>
           <t>11:35</t>
         </is>
@@ -2311,12 +2288,12 @@
       </c>
       <c r="X15" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="Y15" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'패션1Lab'</t>
+        </is>
+      </c>
+      <c r="Y15" s="30" t="inlineStr">
+        <is>
+          <t>누캐시미어 라쿤울 베스트</t>
         </is>
       </c>
       <c r="Z15" s="25"/>
@@ -2453,7 +2430,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="M16" s="39" t="inlineStr">
+      <c r="M16" s="37" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -2506,7 +2483,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="Y16" s="39" t="inlineStr">
+      <c r="Y16" s="37" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -2671,7 +2648,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="S17" s="39" t="inlineStr">
+      <c r="S17" s="37" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -2698,13 +2675,13 @@
           <t>'가전'</t>
         </is>
       </c>
-      <c r="Y17" s="40" t="inlineStr">
+      <c r="Y17" s="35" t="inlineStr">
         <is>
           <t>LG 공기청정기</t>
         </is>
       </c>
       <c r="Z17" s="25"/>
-      <c r="AA17" s="37" t="inlineStr">
+      <c r="AA17" s="29" t="inlineStr">
         <is>
           <t>14:35</t>
         </is>
@@ -2716,17 +2693,17 @@
       </c>
       <c r="AC17" s="24" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>중</t>
         </is>
       </c>
       <c r="AD17" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AE17" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>P.D.Lab</t>
+        </is>
+      </c>
+      <c r="AE17" s="30" t="inlineStr">
+        <is>
+          <t>알레보 프라이팬</t>
         </is>
       </c>
       <c r="AF17" s="25"/>
@@ -2775,12 +2752,12 @@
       </c>
       <c r="AP17" s="30" t="inlineStr">
         <is>
-          <t>'리빙'</t>
+          <t>'뷰티브랜드'</t>
         </is>
       </c>
       <c r="AQ17" s="30" t="inlineStr">
         <is>
-          <t>플로너스디퓨저</t>
+          <t>더마픽스 마스크팩</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2810,7 @@
 수</t>
         </is>
       </c>
-      <c r="L18" s="41" t="inlineStr">
+      <c r="L18" s="38" t="inlineStr">
         <is>
           <t>'리빙'</t>
         </is>
@@ -2891,13 +2868,13 @@
           <t>'가전'</t>
         </is>
       </c>
-      <c r="Y18" s="40" t="inlineStr">
+      <c r="Y18" s="35" t="inlineStr">
         <is>
           <t>LG 건조기</t>
         </is>
       </c>
       <c r="Z18" s="25"/>
-      <c r="AA18" s="37" t="inlineStr">
+      <c r="AA18" s="29" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
@@ -2914,12 +2891,12 @@
       </c>
       <c r="AD18" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AE18" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'패션4Lab'</t>
+        </is>
+      </c>
+      <c r="AE18" s="30" t="inlineStr">
+        <is>
+          <t>라일앤스콧 26FW 론칭</t>
         </is>
       </c>
       <c r="AF18" s="25"/>
@@ -3082,7 +3059,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="Y19" s="39" t="inlineStr">
+      <c r="Y19" s="37" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -3245,7 +3222,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="S20" s="39" t="inlineStr">
+      <c r="S20" s="37" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -3278,7 +3255,7 @@
         </is>
       </c>
       <c r="Z20" s="25"/>
-      <c r="AA20" s="37" t="inlineStr">
+      <c r="AA20" s="29" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
@@ -3288,19 +3265,20 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AC20" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="AC20" s="31" t="inlineStr">
+        <is>
+          <t>수
+수</t>
         </is>
       </c>
       <c r="AD20" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AE20" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'가전'</t>
+        </is>
+      </c>
+      <c r="AE20" s="30" t="inlineStr">
+        <is>
+          <t>다이슨디지털슬림청소기</t>
         </is>
       </c>
       <c r="AF20" s="25"/>
@@ -3351,7 +3329,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="AQ20" s="39" t="inlineStr">
+      <c r="AQ20" s="37" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -3411,7 +3389,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="M21" s="42" t="inlineStr">
+      <c r="M21" s="39" t="inlineStr">
         <is>
           <t>해남 호박고구마</t>
         </is>
@@ -3576,7 +3554,7 @@
           <t>'리빙'</t>
         </is>
       </c>
-      <c r="G22" s="42" t="inlineStr">
+      <c r="G22" s="39" t="inlineStr">
         <is>
           <t>팀P-프로쉬 주방세제</t>
         </is>
@@ -3770,7 +3748,7 @@
           <t>P.D.Lab</t>
         </is>
       </c>
-      <c r="G23" s="42" t="inlineStr">
+      <c r="G23" s="39" t="inlineStr">
         <is>
           <t>팀P-알레보 유리 밥용기</t>
         </is>
@@ -3796,7 +3774,7 @@
           <t>'주방'</t>
         </is>
       </c>
-      <c r="M23" s="42" t="inlineStr">
+      <c r="M23" s="39" t="inlineStr">
         <is>
           <t>사업부P-브리타 정수기</t>
         </is>
@@ -3928,7 +3906,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="AQ23" s="39" t="inlineStr">
+      <c r="AQ23" s="37" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -3961,7 +3939,7 @@
           <t>'가전'</t>
         </is>
       </c>
-      <c r="G24" s="42" t="inlineStr">
+      <c r="G24" s="39" t="inlineStr">
         <is>
           <t>황쇼 다이슨에어랩</t>
         </is>
@@ -3987,7 +3965,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="M24" s="42" t="inlineStr">
+      <c r="M24" s="39" t="inlineStr">
         <is>
           <t>후버 토마토주스</t>
         </is>
@@ -4042,7 +4020,7 @@
       </c>
       <c r="Y24" s="30" t="inlineStr">
         <is>
-          <t>미세스문 다이아모달 침구</t>
+          <t>해즈픽칫솔</t>
         </is>
       </c>
       <c r="Z24" s="25"/>
@@ -4066,7 +4044,7 @@
           <t>'GA'</t>
         </is>
       </c>
-      <c r="AE24" s="39" t="inlineStr">
+      <c r="AE24" s="37" t="inlineStr">
         <is>
           <t>#금융GA</t>
         </is>
@@ -4098,7 +4076,7 @@
         </is>
       </c>
       <c r="AL24" s="25"/>
-      <c r="AM24" s="37" t="inlineStr">
+      <c r="AM24" s="29" t="inlineStr">
         <is>
           <t>23:50</t>
         </is>
@@ -4108,19 +4086,20 @@
           <t>70</t>
         </is>
       </c>
-      <c r="AO24" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
+      <c r="AO24" s="31" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="AP24" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AQ24" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'레포츠'</t>
+        </is>
+      </c>
+      <c r="AQ24" s="30" t="inlineStr">
+        <is>
+          <t>아이그너</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4156,7 @@
           <t>'액티브라이프'</t>
         </is>
       </c>
-      <c r="M25" s="42" t="inlineStr">
+      <c r="M25" s="39" t="inlineStr">
         <is>
           <t>전국한우협회 한우스테이크</t>
         </is>
@@ -4262,7 +4241,7 @@
         </is>
       </c>
       <c r="AF25" s="25"/>
-      <c r="AG25" s="37" t="inlineStr">
+      <c r="AG25" s="29" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
@@ -4279,12 +4258,12 @@
       </c>
       <c r="AJ25" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AK25" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'뷰티1'</t>
+        </is>
+      </c>
+      <c r="AK25" s="33" t="inlineStr">
+        <is>
+          <t>히말라야 수분크림</t>
         </is>
       </c>
       <c r="AL25" s="25"/>
@@ -4321,7 +4300,7 @@
         </is>
       </c>
       <c r="B26" s="25"/>
-      <c r="C26" s="37" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
         <is>
           <t>22:55</t>
         </is>
@@ -4333,17 +4312,17 @@
       </c>
       <c r="E26" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>대</t>
         </is>
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="G26" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'국내여행'</t>
+        </is>
+      </c>
+      <c r="G26" s="30" t="inlineStr">
+        <is>
+          <t>용평리조트</t>
         </is>
       </c>
       <c r="H26" s="25"/>
@@ -4426,7 +4405,7 @@
         </is>
       </c>
       <c r="Z26" s="25"/>
-      <c r="AA26" s="37" t="inlineStr">
+      <c r="AA26" s="29" t="inlineStr">
         <is>
           <t>00:35</t>
         </is>
@@ -4438,21 +4417,21 @@
       </c>
       <c r="AC26" s="24" t="inlineStr">
         <is>
-          <t>대</t>
+          <t>수</t>
         </is>
       </c>
       <c r="AD26" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AE26" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'잡화'</t>
+        </is>
+      </c>
+      <c r="AE26" s="33" t="inlineStr">
+        <is>
+          <t>스케쳐스 고워크 아웃도어</t>
         </is>
       </c>
       <c r="AF26" s="25"/>
-      <c r="AG26" s="37" t="inlineStr">
+      <c r="AG26" s="29" t="inlineStr">
         <is>
           <t>23:30</t>
         </is>
@@ -4462,19 +4441,20 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AI26" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
+      <c r="AI26" s="31" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="AJ26" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AK26" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'가전'</t>
+        </is>
+      </c>
+      <c r="AK26" s="30" t="inlineStr">
+        <is>
+          <t>쥬베라 마사지기</t>
         </is>
       </c>
       <c r="AL26" s="25"/>
@@ -4495,7 +4475,7 @@
         </is>
       </c>
       <c r="B27" s="25"/>
-      <c r="C27" s="37" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
         <is>
           <t>23:55</t>
         </is>
@@ -4512,16 +4492,16 @@
       </c>
       <c r="F27" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="G27" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'주얼리'</t>
+        </is>
+      </c>
+      <c r="G27" s="30" t="inlineStr">
+        <is>
+          <t>골드라벨 24K</t>
         </is>
       </c>
       <c r="H27" s="25"/>
-      <c r="I27" s="37" t="inlineStr">
+      <c r="I27" s="29" t="inlineStr">
         <is>
           <t>22:55</t>
         </is>
@@ -4538,12 +4518,12 @@
       </c>
       <c r="L27" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="M27" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'패션3Lab'</t>
+        </is>
+      </c>
+      <c r="M27" s="30" t="inlineStr">
+        <is>
+          <t>머티리얼랩 레이스 니트 집업 外</t>
         </is>
       </c>
       <c r="N27" s="25"/>
@@ -4627,7 +4607,7 @@
         </is>
       </c>
       <c r="AF27" s="25"/>
-      <c r="AG27" s="37" t="inlineStr">
+      <c r="AG27" s="29" t="inlineStr">
         <is>
           <t>00:30</t>
         </is>
@@ -4637,19 +4617,20 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AI27" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
+      <c r="AI27" s="31" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="AJ27" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AK27" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'리빙'</t>
+        </is>
+      </c>
+      <c r="AK27" s="30" t="inlineStr">
+        <is>
+          <t>메종노아 양모침구</t>
         </is>
       </c>
       <c r="AL27" s="25"/>
@@ -4716,13 +4697,13 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="M28" s="39" t="inlineStr">
+      <c r="M28" s="37" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
       </c>
       <c r="N28" s="25"/>
-      <c r="O28" s="37" t="inlineStr">
+      <c r="O28" s="29" t="inlineStr">
         <is>
           <t>23:55</t>
         </is>
@@ -4734,17 +4715,17 @@
       </c>
       <c r="Q28" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>대</t>
         </is>
       </c>
       <c r="R28" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="S28" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'GA'</t>
+        </is>
+      </c>
+      <c r="S28" s="37" t="inlineStr">
+        <is>
+          <t>#금융GA</t>
         </is>
       </c>
       <c r="T28" s="25"/>
